--- a/diseases/d042/1995-1999.xlsx
+++ b/diseases/d042/1995-1999.xlsx
@@ -11303,6 +11303,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12228,6 +12233,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12763,6 +12773,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13298,6 +13313,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13833,6 +13853,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14368,6 +14393,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14903,6 +14933,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15438,6 +15473,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15973,6 +16013,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16508,6 +16553,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17043,6 +17093,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17578,6 +17633,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18503,6 +18563,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19038,6 +19103,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19183,6 +19253,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19328,6 +19403,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19473,6 +19553,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19618,6 +19703,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19763,6 +19853,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19908,6 +20003,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20053,6 +20153,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20198,6 +20303,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20343,6 +20453,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20488,6 +20603,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21023,6 +21143,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21558,6 +21683,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21703,6 +21833,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21848,6 +21983,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21993,6 +22133,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22138,6 +22283,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22283,6 +22433,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22428,6 +22583,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22573,6 +22733,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22718,6 +22883,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22863,6 +23033,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23006,6 +23181,11 @@
       <c r="S125" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">

--- a/diseases/d042/1995-1999.xlsx
+++ b/diseases/d042/1995-1999.xlsx
@@ -11298,6 +11298,11 @@
       <c r="Q56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11310,12 +11315,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -12213,6 +12228,11 @@
       <c r="Q61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12225,12 +12245,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -12738,6 +12768,11 @@
       <c r="Q64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12750,12 +12785,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -13263,6 +13308,11 @@
       <c r="Q67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13275,12 +13325,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -13788,6 +13848,11 @@
       <c r="Q70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13800,12 +13865,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -14313,6 +14388,11 @@
       <c r="Q73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14325,12 +14405,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -14838,6 +14928,11 @@
       <c r="Q76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14850,12 +14945,22 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -15363,6 +15468,11 @@
       <c r="Q79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15375,12 +15485,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -15888,6 +16008,11 @@
       <c r="Q82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15900,12 +16025,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -16413,6 +16548,11 @@
       <c r="Q85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16425,12 +16565,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -16938,6 +17088,11 @@
       <c r="Q88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16950,12 +17105,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -17463,6 +17628,11 @@
       <c r="Q91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17475,12 +17645,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -18378,6 +18558,11 @@
       <c r="Q96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18390,12 +18575,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -18903,6 +19098,11 @@
       <c r="Q99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18915,12 +19115,22 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -19038,6 +19248,11 @@
       <c r="Q100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19050,12 +19265,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -19173,6 +19398,11 @@
       <c r="Q101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19185,12 +19415,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -19308,6 +19548,11 @@
       <c r="Q102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19320,12 +19565,22 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -19443,6 +19698,11 @@
       <c r="Q103" t="n">
         <v>0</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19455,12 +19715,22 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -19578,6 +19848,11 @@
       <c r="Q104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19590,12 +19865,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -19713,6 +19998,11 @@
       <c r="Q105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19725,12 +20015,22 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -19848,6 +20148,11 @@
       <c r="Q106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19860,12 +20165,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -19983,6 +20298,11 @@
       <c r="Q107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19995,12 +20315,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -20118,6 +20448,11 @@
       <c r="Q108" t="n">
         <v>0</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20130,12 +20465,22 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -20253,6 +20598,11 @@
       <c r="Q109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20265,12 +20615,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -20778,6 +21138,11 @@
       <c r="Q112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20790,12 +21155,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -21303,6 +21678,11 @@
       <c r="Q115" t="n">
         <v>0</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21315,12 +21695,22 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -21438,6 +21828,11 @@
       <c r="Q116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21450,12 +21845,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -21573,6 +21978,11 @@
       <c r="Q117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21585,12 +21995,22 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -21708,6 +22128,11 @@
       <c r="Q118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21720,12 +22145,22 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -21843,6 +22278,11 @@
       <c r="Q119" t="n">
         <v>0</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21855,12 +22295,22 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -21978,6 +22428,11 @@
       <c r="Q120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21990,12 +22445,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -22113,6 +22578,11 @@
       <c r="Q121" t="n">
         <v>0</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22125,12 +22595,22 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -22248,6 +22728,11 @@
       <c r="Q122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22260,12 +22745,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -22383,6 +22878,11 @@
       <c r="Q123" t="n">
         <v>0</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22395,12 +22895,22 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -22518,6 +23028,11 @@
       <c r="Q124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22530,12 +23045,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -22653,6 +23178,11 @@
       <c r="Q125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22665,12 +23195,22 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
